--- a/data/all_datasets/REDD/REDD_House6_stats/2026-04-13.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-04-13.xlsx
@@ -22275,7 +22275,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -23287,7 +23287,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E51" t="n">
